--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/01_business_functions.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/01_business_functions.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R3f2050d65b364068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rff96466569564505"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Ra2c59f61c1de496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rd877ae0b559e4d12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R5d6496ce3c1e4ac7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rc8c08bf153d8444e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R8021c39a4025449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Ra1dc9203304448eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R913704efe1714414"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R9de5f74fc3bb4892"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R45b4215c281a4cbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R8ba3596a5946485d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -624,7 +624,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d1a16452d8c4358"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1dda03ad341d4f74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -785,7 +785,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M6" s="80" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Executive Office (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -829,7 +829,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M7" s="81" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Retail Deposits and Branch Operations (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N7" s="43" t="str">
         <x:v>High</x:v>
@@ -873,7 +873,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M8" s="82" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Commercial Lending and Treasury (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N8" s="45" t="str">
         <x:v>High</x:v>
@@ -917,7 +917,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M9" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Cards Operations (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N9" t="str">
         <x:v>High</x:v>
@@ -961,7 +961,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M10" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments Operations (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N10" t="str">
         <x:v>High</x:v>
@@ -1005,7 +1005,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M11" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Consumer Lending Operations (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N11" t="str">
         <x:v>Medium</x:v>
@@ -1049,7 +1049,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M12" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Wealth Advisory and Brokerage (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N12" t="str">
         <x:v>High</x:v>
@@ -1093,7 +1093,7 @@
         <x:v>Critical</x:v>
       </x:c>
       <x:c r="M13" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Fraud and Risk Operations (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N13" t="str">
         <x:v>High</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M14" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Compliance and Model Risk Management (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N14" t="str">
         <x:v>High</x:v>
@@ -1181,7 +1181,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M15" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact Center and Servicing (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N15" t="str">
         <x:v>High</x:v>
@@ -1225,7 +1225,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M16" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N16" t="str">
         <x:v>Medium</x:v>
@@ -1269,7 +1269,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M17" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Core Banking Modernization (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N17" t="str">
         <x:v>High</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M18" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Customer 360 Data Product (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N18" t="str">
         <x:v>High</x:v>
@@ -1357,7 +1357,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M19" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile Retail Banking Analytics (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N19" t="str">
         <x:v>High</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M20" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards Portfolio Analytics (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N20" t="str">
         <x:v>High</x:v>
@@ -1445,7 +1445,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M21" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Payments and Settlement Analytics (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N21" t="str">
         <x:v>Medium</x:v>
@@ -1489,7 +1489,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M22" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Fraud and Risk Analytics (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="N22" t="str">
         <x:v>High</x:v>
@@ -1533,7 +1533,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M23" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Attach client evidence for Cloud Data Platform (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="N23" t="str">
         <x:v>High</x:v>
@@ -1577,7 +1577,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M24" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Reconcile IT Budget and Tower Baseline (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="N24" t="str">
         <x:v>High</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M25" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor and Contract Optimization (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="N25" t="str">
         <x:v>High</x:v>
@@ -1665,7 +1665,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M26" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Validate Infrastructure and CMDB (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for business functions.</x:v>
       </x:c>
       <x:c r="N26" t="str">
         <x:v>Medium</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>High</x:v>
       </x:c>
       <x:c r="M27" t="str">
-        <x:v>Confirm process volumes, named process owners, system-of-record boundaries, and decision rights in workshop.</x:v>
+        <x:v>Confirm Incident Problem Change Operations (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this business functions record is used downstream.</x:v>
       </x:c>
       <x:c r="N27" t="str">
         <x:v>High</x:v>
@@ -1736,7 +1736,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref8c0b118ab54f1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e04f8fba1784726"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1866,7 +1866,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red1dc79c34534c36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71cc4911da044943"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2084,7 +2084,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7629ecacfb884350"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re866994706164e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2162,7 +2162,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd594d190d94742ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf28e38d7798b4c65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2272,7 +2272,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbff37ca4dbaf4d1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a7ffaf2b1274665"/>
   </x:tableParts>
 </x:worksheet>
 </file>